--- a/data/lore.xlsx
+++ b/data/lore.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Lore" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="_Tree Index" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lore" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -582,16 +582,16 @@
           <t>x</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr"/>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
           <t>You are Trained in this Lore: add the Constellation's rank to its checks. Recall and research within its field; you know its people, texts, and secrets. Every talent here requires this.</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -604,26 +604,26 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr"/>
+      <c r="C3" s="2" t="n"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
           <t>Deep Knowledge</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>+2 circumstance to any check where you can explain how this field directly applies. The GM is the judge; the story is the proof.</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>+2 Situation to any check where you can explain how this field directly applies. The GM is the judge; the story is the proof.</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Well Read ◇</t>
+          <t>Well Read ⓿</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -631,21 +631,21 @@
           <t>T</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
+      <c r="C4" s="2" t="n"/>
       <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Deep Knowledge</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Once per scene, Recall Knowledge about your field as a free action.</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
+          <t>Once per scene, Recall Knowledge ⓿ about your field.</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n"/>
+      <c r="I4" s="2" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/lore.xlsx
+++ b/data/lore.xlsx
@@ -505,7 +505,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -517,6 +517,7 @@
     <col width="96" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -563,6 +564,11 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Grants (restricted TPs this talent gives)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Aura (15 ft, 15 ft allies, 15 ft enemies, add visible to pin it by default, or none)</t>
         </is>
       </c>
     </row>
